--- a/artfynd/A 48343-2022 artfynd.xlsx
+++ b/artfynd/A 48343-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48343-2022 artfynd.xlsx
+++ b/artfynd/A 48343-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,70 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111545414</v>
+        <v>7095635</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orsa Viborg, glänta i mitten av skogsparti, Dlr</t>
+          <t>Wixnersvägen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480487.2503558649</v>
+        <v>480377</v>
       </c>
       <c r="R2" t="n">
-        <v>6772784.264016891</v>
+        <v>6772781</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>22:30</t>
+          <t>2010-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>03:30</t>
+          <t>2010-07-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>överkörd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,57 +776,56 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111543968</v>
+        <v>111543957</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -857,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480406.6045043401</v>
+        <v>480407</v>
       </c>
       <c r="R3" t="n">
-        <v>6772745.04339793</v>
+        <v>6772746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -929,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111543957</v>
+        <v>111545328</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,11 +945,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -982,14 +956,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orsa Viborg, glänta i skogsparti, Dlr</t>
+          <t>Orsa Viborg, intill en grupp med hålträd, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480406.6045043401</v>
+        <v>480428</v>
       </c>
       <c r="R4" t="n">
-        <v>6772745.04339793</v>
+        <v>6772811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1058,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111545323</v>
+        <v>111543968</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1107,14 +1076,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orsa Viborg, intill en grupp med hålträd, Dlr</t>
+          <t>Orsa Viborg, glänta i skogsparti, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480427.8053356989</v>
+        <v>480407</v>
       </c>
       <c r="R5" t="n">
-        <v>6772811.198980245</v>
+        <v>6772746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1183,15 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111545401</v>
+        <v>111545323</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,14 +1182,10 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1236,14 +1196,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orsa Viborg, glänta i mitten av skogsparti, Dlr</t>
+          <t>Orsa Viborg, intill en grupp med hålträd, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480487.2503558649</v>
+        <v>480428</v>
       </c>
       <c r="R6" t="n">
-        <v>6772784.264016891</v>
+        <v>6772811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,15 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111545328</v>
+        <v>111545414</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,10 +1302,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1361,14 +1320,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orsa Viborg, intill en grupp med hålträd, Dlr</t>
+          <t>Orsa Viborg, glänta i mitten av skogsparti, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480427.8053356989</v>
+        <v>480487</v>
       </c>
       <c r="R7" t="n">
-        <v>6772811.198980245</v>
+        <v>6772784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,6 +1393,130 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111545401</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Orsa Viborg, glänta i mitten av skogsparti, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480487</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6772784</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48343-2022 artfynd.xlsx
+++ b/artfynd/A 48343-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7095635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111543957</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111545328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111545414</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,6 +1298,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111543968</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111545323</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,8 +1552,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111545401</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>